--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1274_2021</t>
+          <t>1274_2022</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1274</v>
       </c>
       <c r="D3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E3" t="n">
-        <v>798.8118518518518</v>
+        <v>890.1531837376832</v>
       </c>
       <c r="F3" t="n">
-        <v>53.8111111111111</v>
+        <v>33.95959261405978</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06736393680985463</v>
+        <v>0.03815027933896289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5149713238063</v>
+        <v>0.5171496395612585</v>
       </c>
       <c r="I3" t="n">
-        <v>0.970171</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.206153</v>
+        <v>0.314421</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -500,10 +500,10 @@
         <v>0.03069684069011875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3113050186609954</v>
+        <v>0.3113082136533404</v>
       </c>
       <c r="I2" t="n">
-        <v>0.651114</v>
+        <v>0.65111</v>
       </c>
       <c r="J2" t="n">
         <v>-3.189392</v>

--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -532,13 +532,13 @@
         <v>2022</v>
       </c>
       <c r="E3" t="n">
-        <v>890.1531837376832</v>
+        <v>890.1631199801275</v>
       </c>
       <c r="F3" t="n">
         <v>33.95959261405978</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03815027933896289</v>
+        <v>0.03814985349518627</v>
       </c>
       <c r="H3" t="n">
         <v>0.5171496395612585</v>
@@ -547,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.314421</v>
+        <v>0.314432</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -481,32 +481,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1729_2016</t>
+          <t>6105_2015</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1729</v>
+        <v>6105</v>
       </c>
       <c r="D2" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E2" t="n">
-        <v>26.778</v>
+        <v>15.069</v>
       </c>
       <c r="F2" t="n">
-        <v>0.822</v>
+        <v>0.284</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03069684069011875</v>
+        <v>0.0188466387948769</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3113082136533404</v>
+        <v>0.2302810886259073</v>
       </c>
       <c r="I2" t="n">
-        <v>0.65111</v>
+        <v>0.7671559999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.189392</v>
+        <v>-3.764333</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1274_2022</t>
+          <t>1274_2023</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1274</v>
       </c>
       <c r="D3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" t="n">
-        <v>890.1631199801275</v>
+        <v>843.6302283606686</v>
       </c>
       <c r="F3" t="n">
-        <v>33.95959261405978</v>
+        <v>46.05822804677078</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03814985349518627</v>
+        <v>0.05459527942268087</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5171496395612585</v>
+        <v>0.4933871824899816</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.970257</v>
       </c>
       <c r="J3" t="n">
-        <v>0.314432</v>
+        <v>0.260742</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1274_2023</t>
+          <t>1884_2022</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1274</v>
+        <v>1884</v>
       </c>
       <c r="D3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E3" t="n">
-        <v>843.6302283606686</v>
+        <v>642.193</v>
       </c>
       <c r="F3" t="n">
-        <v>46.05822804677078</v>
+        <v>9.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05459527942268087</v>
+        <v>0.01417019494139612</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4933871824899816</v>
+        <v>0.9802235265502031</v>
       </c>
       <c r="I3" t="n">
-        <v>0.970257</v>
+        <v>0.972245</v>
       </c>
       <c r="J3" t="n">
-        <v>0.260742</v>
+        <v>-0.012083</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -500,10 +500,10 @@
         <v>0.0188466387948769</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2302810886259073</v>
+        <v>0.2507695995042568</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7671559999999999</v>
+        <v>0.775564</v>
       </c>
       <c r="J2" t="n">
         <v>-3.764333</v>
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1884_2022</t>
+          <t>1274_2022</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1884</v>
+        <v>1274</v>
       </c>
       <c r="D3" t="n">
         <v>2022</v>
       </c>
       <c r="E3" t="n">
-        <v>642.193</v>
+        <v>890.1631199801275</v>
       </c>
       <c r="F3" t="n">
-        <v>9.1</v>
+        <v>33.95959261405978</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01417019494139612</v>
+        <v>0.03814985349518627</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9802235265502031</v>
+        <v>0.5171496395612585</v>
       </c>
       <c r="I3" t="n">
-        <v>0.972245</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.012083</v>
+        <v>0.314432</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -535,10 +535,10 @@
         <v>890.1631199801275</v>
       </c>
       <c r="F3" t="n">
-        <v>33.95959261405978</v>
+        <v>7.419061025089013</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03814985349518627</v>
+        <v>0.008334496069950235</v>
       </c>
       <c r="H3" t="n">
         <v>0.5171496395612585</v>
